--- a/static/files/DMAX-2024-Live.xlsx
+++ b/static/files/DMAX-2024-Live.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A157E77A-6399-4A86-992C-E3CF2867E8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E5192-6926-415D-9FDF-1966282813B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,10 +343,10 @@
     <t>yy@qaoncloud.com</t>
   </si>
   <si>
-    <t>Sr.QA Engineer</t>
+    <t>Fora Travels</t>
   </si>
   <si>
-    <t>Fora Travels</t>
+    <t>Intern</t>
   </si>
 </sst>
 </file>
@@ -763,60 +763,13 @@
     <xf numFmtId="10" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -907,6 +860,60 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -925,13 +932,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1201,201 +1201,201 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="23.4" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="45" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="54" t="s">
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="80"/>
+      <c r="AI1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="56"/>
-      <c r="AS1" s="60" t="s">
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="AT1" s="61"/>
-      <c r="AU1" s="61"/>
-      <c r="AV1" s="61"/>
-      <c r="AW1" s="61"/>
-      <c r="AX1" s="61"/>
-      <c r="AY1" s="61"/>
-      <c r="AZ1" s="61"/>
-      <c r="BA1" s="61"/>
-      <c r="BB1" s="61"/>
-      <c r="BC1" s="61"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="66" t="s">
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
+      <c r="AV1" s="46"/>
+      <c r="AW1" s="46"/>
+      <c r="AX1" s="46"/>
+      <c r="AY1" s="46"/>
+      <c r="AZ1" s="46"/>
+      <c r="BA1" s="46"/>
+      <c r="BB1" s="46"/>
+      <c r="BC1" s="46"/>
+      <c r="BD1" s="47"/>
+      <c r="BE1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="BF1" s="67"/>
-      <c r="BG1" s="67"/>
-      <c r="BH1" s="68"/>
-      <c r="BI1" s="72" t="s">
+      <c r="BF1" s="52"/>
+      <c r="BG1" s="52"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="73"/>
-      <c r="BK1" s="74"/>
-      <c r="BL1" s="78" t="s">
+      <c r="BJ1" s="58"/>
+      <c r="BK1" s="59"/>
+      <c r="BL1" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="79"/>
-      <c r="BN1" s="80"/>
-      <c r="BO1" s="39" t="s">
+      <c r="BM1" s="82"/>
+      <c r="BN1" s="83"/>
+      <c r="BO1" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="39" t="s">
+      <c r="BP1" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="BQ1" s="39" t="s">
+      <c r="BQ1" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="41" t="s">
+      <c r="BR1" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="43" t="s">
+      <c r="BS1" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="BT1" s="30" t="s">
+      <c r="BT1" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="BU1" s="31"/>
-      <c r="BV1" s="31"/>
-      <c r="BW1" s="31"/>
-      <c r="BX1" s="31"/>
-      <c r="BY1" s="32"/>
+      <c r="BU1" s="64"/>
+      <c r="BV1" s="64"/>
+      <c r="BW1" s="64"/>
+      <c r="BX1" s="64"/>
+      <c r="BY1" s="65"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
       <c r="CB1" s="1"/>
     </row>
     <row r="2" spans="1:80" ht="21" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="33" t="s">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="33" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="33" t="s">
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="35"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="68"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="33" t="s">
+      <c r="X2" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="57"/>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AO2" s="58"/>
-      <c r="AP2" s="58"/>
-      <c r="AQ2" s="58"/>
-      <c r="AR2" s="59"/>
-      <c r="AS2" s="63"/>
-      <c r="AT2" s="64"/>
-      <c r="AU2" s="64"/>
-      <c r="AV2" s="64"/>
-      <c r="AW2" s="64"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="64"/>
-      <c r="BA2" s="64"/>
-      <c r="BB2" s="64"/>
-      <c r="BC2" s="64"/>
-      <c r="BD2" s="65"/>
-      <c r="BE2" s="69"/>
-      <c r="BF2" s="70"/>
-      <c r="BG2" s="70"/>
-      <c r="BH2" s="71"/>
-      <c r="BI2" s="75"/>
-      <c r="BJ2" s="76"/>
-      <c r="BK2" s="77"/>
-      <c r="BL2" s="81"/>
-      <c r="BM2" s="82"/>
-      <c r="BN2" s="83"/>
-      <c r="BO2" s="40"/>
-      <c r="BP2" s="40"/>
-      <c r="BQ2" s="40"/>
-      <c r="BR2" s="42"/>
-      <c r="BS2" s="44"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="67"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="48"/>
+      <c r="AT2" s="49"/>
+      <c r="AU2" s="49"/>
+      <c r="AV2" s="49"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="49"/>
+      <c r="AY2" s="49"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="49"/>
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="50"/>
+      <c r="BE2" s="54"/>
+      <c r="BF2" s="55"/>
+      <c r="BG2" s="55"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="61"/>
+      <c r="BK2" s="62"/>
+      <c r="BL2" s="84"/>
+      <c r="BM2" s="85"/>
+      <c r="BN2" s="86"/>
+      <c r="BO2" s="73"/>
+      <c r="BP2" s="73"/>
+      <c r="BQ2" s="73"/>
+      <c r="BR2" s="75"/>
+      <c r="BS2" s="77"/>
       <c r="BT2" s="3"/>
       <c r="BU2" s="4"/>
       <c r="BV2" s="5"/>
-      <c r="BW2" s="36" t="s">
+      <c r="BW2" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="BX2" s="37"/>
-      <c r="BY2" s="38"/>
+      <c r="BX2" s="70"/>
+      <c r="BY2" s="71"/>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1"/>
       <c r="CB2" s="1"/>
@@ -1627,23 +1627,23 @@
       <c r="CB3" s="1"/>
     </row>
     <row r="4" spans="1:80" ht="13.8">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="F4" s="84" t="s">
-        <v>92</v>
       </c>
       <c r="G4" s="22">
         <v>60</v>
@@ -1824,7 +1824,7 @@
         <f t="shared" ref="BM4" si="1">SUM(H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4,AB4,AD4,AF4,AH4,AJ4,AL4,AN4,AP4,AR4,AT4,AV4,AX4,AZ4,BB4,BD4)</f>
         <v>8</v>
       </c>
-      <c r="BN4" s="17" t="e" cm="1">
+      <c r="BN4" s="17" cm="1">
         <f t="array" ref="BN4">_xlfn.IFS(
    F4="Intern", IFERROR(BM4/BL4*30/100, 0),
    F4="SrQAEngineer", IFERROR(BM4/BL4*30/100, 0),
@@ -1832,9 +1832,9 @@
    F4="QAEngineer", IFERROR(BM4/BL4*35/100, 0),
    F4="QALead", IFERROR(BM4/BL4*20/100, 0)
 )</f>
-        <v>#N/A</v>
+        <v>3.6923076923076927E-2</v>
       </c>
-      <c r="BO4" s="17" t="e" cm="1">
+      <c r="BO4" s="17" cm="1">
         <f t="array" ref="BO4">_xlfn.IFS(
    F4="Intern", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.5 / 100, 0),
    F4="JrQAEngineer", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.4 / 100, 0),
@@ -1842,23 +1842,23 @@
    F4="SrQAEngineer", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.4 / 100, 0),
    F4="QALead", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.4 / 100, 0)
 )</f>
-        <v>#N/A</v>
+        <v>0.5</v>
       </c>
-      <c r="BP4" s="17" t="e" cm="1">
+      <c r="BP4" s="17" cm="1">
         <f t="array" ref="BP4">_xlfn.IFS(F4="Intern", (BI4*1)*10/100, F4="JrQAEngineer", (BI4*1)*10/100, F4="QAEngineer", (BI4*1)*5/100, F4="SrQAEngineer", (BI4*1)*5/100, F4="QALead", (BI4*1)*5/100)</f>
-        <v>#N/A</v>
+        <v>0.1</v>
       </c>
-      <c r="BQ4" s="17" t="e" cm="1">
+      <c r="BQ4" s="17" cm="1">
         <f t="array" ref="BQ4">_xlfn.IFS(F4="Intern", IF(BI4&gt;=0.5, BJ4*10/100/100, 0), F4="JrQAEngineer", IF(BI4&gt;=0.5, BJ4*10/100/100, 0), F4="QAEngineer", IF(BI4&gt;=0.5, BJ4*5/100/100, 0), F4="SrQAEngineer", IF(BI4&gt;=0.5, BJ4*5/100/100, 0), F4="QALead", IF(BI4&gt;=0.5, BJ4*5/100/100, 0))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
-      <c r="BR4" s="17" t="e" cm="1">
+      <c r="BR4" s="17" cm="1">
         <f t="array" ref="BR4">_xlfn.IFS(F4="Intern", IF(BI4&gt;=0.5, BK4*0/100/100, 0), F4="JrQAEngineer", IF(BI4&gt;=0.5, BK4*0/100/100, 0), F4="QAEngineer", IF(BI4&gt;=0.5, BK4*15/100/100, 0), F4="SrQAEngineer", IF(BI4&gt;=0.5, BK4*20/100/100, 0), F4="QALead", IF(BI4&gt;=0.5, BK4*30/100/100, 0))</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
-      <c r="BS4" s="17" t="e">
+      <c r="BS4" s="17">
         <f t="shared" ref="BS4" si="2">SUM(BN4:BR4)</f>
-        <v>#N/A</v>
+        <v>0.63692307692307693</v>
       </c>
     </row>
     <row r="5" spans="1:80" ht="13.2">
@@ -28088,11 +28088,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="AI1:AR2"/>
-    <mergeCell ref="AS1:BD2"/>
-    <mergeCell ref="BE1:BH2"/>
-    <mergeCell ref="BI1:BK2"/>
     <mergeCell ref="BT1:BY1"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="M2:P2"/>
@@ -28106,13 +28101,15 @@
     <mergeCell ref="BS1:BS2"/>
     <mergeCell ref="G1:AH1"/>
     <mergeCell ref="BL1:BN2"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="AI1:AR2"/>
+    <mergeCell ref="AS1:BD2"/>
+    <mergeCell ref="BE1:BH2"/>
+    <mergeCell ref="BI1:BK2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
       <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{127724BC-49DF-4768-A231-099C7CD25DD7}">
-      <formula1>"Intern,Jr.QA Engineer,QA Engineer,Sr.QA Engineer,QA Lead"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/static/files/DMAX-2024-Live.xlsx
+++ b/static/files/DMAX-2024-Live.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E5192-6926-415D-9FDF-1966282813B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A509B-3F14-40B8-A2B9-9F5C6516B5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>Basic Information</t>
   </si>
@@ -331,22 +331,19 @@
     <t>Blank</t>
   </si>
   <si>
-    <t>Test</t>
+    <t>Intern</t>
   </si>
   <si>
-    <t>DC000</t>
+    <t>Tanushree</t>
   </si>
   <si>
-    <t>dd-mm-yy</t>
+    <t>DC4771</t>
   </si>
   <si>
-    <t>yy@qaoncloud.com</t>
+    <t>Suganya@qaoncloud.com</t>
   </si>
   <si>
-    <t>Fora Travels</t>
-  </si>
-  <si>
-    <t>Intern</t>
+    <t>Indihood</t>
   </si>
 </sst>
 </file>
@@ -357,7 +354,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -452,6 +449,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -684,7 +687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,10 +769,79 @@
     <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -860,76 +932,10 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1201,201 +1207,201 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="23.4" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="78" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="80"/>
-      <c r="AI1" s="39" t="s">
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="45" t="s">
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="64"/>
+      <c r="AS1" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
-      <c r="AV1" s="46"/>
-      <c r="AW1" s="46"/>
-      <c r="AX1" s="46"/>
-      <c r="AY1" s="46"/>
-      <c r="AZ1" s="46"/>
-      <c r="BA1" s="46"/>
-      <c r="BB1" s="46"/>
-      <c r="BC1" s="46"/>
-      <c r="BD1" s="47"/>
-      <c r="BE1" s="51" t="s">
+      <c r="AT1" s="69"/>
+      <c r="AU1" s="69"/>
+      <c r="AV1" s="69"/>
+      <c r="AW1" s="69"/>
+      <c r="AX1" s="69"/>
+      <c r="AY1" s="69"/>
+      <c r="AZ1" s="69"/>
+      <c r="BA1" s="69"/>
+      <c r="BB1" s="69"/>
+      <c r="BC1" s="69"/>
+      <c r="BD1" s="70"/>
+      <c r="BE1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="BF1" s="52"/>
-      <c r="BG1" s="52"/>
-      <c r="BH1" s="53"/>
-      <c r="BI1" s="57" t="s">
+      <c r="BF1" s="75"/>
+      <c r="BG1" s="75"/>
+      <c r="BH1" s="76"/>
+      <c r="BI1" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="58"/>
-      <c r="BK1" s="59"/>
-      <c r="BL1" s="81" t="s">
+      <c r="BJ1" s="81"/>
+      <c r="BK1" s="82"/>
+      <c r="BL1" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="82"/>
-      <c r="BN1" s="83"/>
-      <c r="BO1" s="72" t="s">
+      <c r="BM1" s="51"/>
+      <c r="BN1" s="52"/>
+      <c r="BO1" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="72" t="s">
+      <c r="BP1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="BQ1" s="72" t="s">
+      <c r="BQ1" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="74" t="s">
+      <c r="BR1" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="76" t="s">
+      <c r="BS1" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="BT1" s="63" t="s">
+      <c r="BT1" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="BU1" s="64"/>
-      <c r="BV1" s="64"/>
-      <c r="BW1" s="64"/>
-      <c r="BX1" s="64"/>
-      <c r="BY1" s="65"/>
+      <c r="BU1" s="33"/>
+      <c r="BV1" s="33"/>
+      <c r="BW1" s="33"/>
+      <c r="BX1" s="33"/>
+      <c r="BY1" s="34"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
       <c r="CB1" s="1"/>
     </row>
     <row r="2" spans="1:80" ht="21" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="66" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="66" t="s">
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="66" t="s">
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="68"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="37"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="66" t="s">
+      <c r="X2" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="67"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="49"/>
-      <c r="AU2" s="49"/>
-      <c r="AV2" s="49"/>
-      <c r="AW2" s="49"/>
-      <c r="AX2" s="49"/>
-      <c r="AY2" s="49"/>
-      <c r="AZ2" s="49"/>
-      <c r="BA2" s="49"/>
-      <c r="BB2" s="49"/>
-      <c r="BC2" s="49"/>
-      <c r="BD2" s="50"/>
-      <c r="BE2" s="54"/>
-      <c r="BF2" s="55"/>
-      <c r="BG2" s="55"/>
-      <c r="BH2" s="56"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="61"/>
-      <c r="BK2" s="62"/>
-      <c r="BL2" s="84"/>
-      <c r="BM2" s="85"/>
-      <c r="BN2" s="86"/>
-      <c r="BO2" s="73"/>
-      <c r="BP2" s="73"/>
-      <c r="BQ2" s="73"/>
-      <c r="BR2" s="75"/>
-      <c r="BS2" s="77"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="65"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
+      <c r="AM2" s="66"/>
+      <c r="AN2" s="66"/>
+      <c r="AO2" s="66"/>
+      <c r="AP2" s="66"/>
+      <c r="AQ2" s="66"/>
+      <c r="AR2" s="67"/>
+      <c r="AS2" s="71"/>
+      <c r="AT2" s="72"/>
+      <c r="AU2" s="72"/>
+      <c r="AV2" s="72"/>
+      <c r="AW2" s="72"/>
+      <c r="AX2" s="72"/>
+      <c r="AY2" s="72"/>
+      <c r="AZ2" s="72"/>
+      <c r="BA2" s="72"/>
+      <c r="BB2" s="72"/>
+      <c r="BC2" s="72"/>
+      <c r="BD2" s="73"/>
+      <c r="BE2" s="77"/>
+      <c r="BF2" s="78"/>
+      <c r="BG2" s="78"/>
+      <c r="BH2" s="79"/>
+      <c r="BI2" s="83"/>
+      <c r="BJ2" s="84"/>
+      <c r="BK2" s="85"/>
+      <c r="BL2" s="53"/>
+      <c r="BM2" s="54"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="42"/>
+      <c r="BP2" s="42"/>
+      <c r="BQ2" s="42"/>
+      <c r="BR2" s="44"/>
+      <c r="BS2" s="46"/>
       <c r="BT2" s="3"/>
       <c r="BU2" s="4"/>
       <c r="BV2" s="5"/>
-      <c r="BW2" s="69" t="s">
+      <c r="BW2" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="BX2" s="70"/>
-      <c r="BY2" s="71"/>
+      <c r="BX2" s="39"/>
+      <c r="BY2" s="40"/>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1"/>
       <c r="CB2" s="1"/>
@@ -1627,23 +1633,23 @@
       <c r="CB3" s="1"/>
     </row>
     <row r="4" spans="1:80" ht="13.8">
-      <c r="A4" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="30" t="s">
+      <c r="A4" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>91</v>
+      </c>
+      <c r="D4" s="87">
+        <v>45707</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>92</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G4" s="22">
         <v>60</v>
@@ -1861,12 +1867,12 @@
         <v>0.63692307692307693</v>
       </c>
     </row>
-    <row r="5" spans="1:80" ht="13.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="20"/>
+    <row r="5" spans="1:80" ht="13.8">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="20"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -28088,6 +28094,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="AI1:AR2"/>
+    <mergeCell ref="AS1:BD2"/>
+    <mergeCell ref="BE1:BH2"/>
+    <mergeCell ref="BI1:BK2"/>
     <mergeCell ref="BT1:BY1"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="M2:P2"/>
@@ -28101,20 +28112,12 @@
     <mergeCell ref="BS1:BS2"/>
     <mergeCell ref="G1:AH1"/>
     <mergeCell ref="BL1:BN2"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="AI1:AR2"/>
-    <mergeCell ref="AS1:BD2"/>
-    <mergeCell ref="BE1:BH2"/>
-    <mergeCell ref="BI1:BK2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E5" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
       <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{65E3908E-8395-4520-A3ED-9E8FE5F94297}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/static/files/DMAX-2024-Live.xlsx
+++ b/static/files/DMAX-2024-Live.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A509B-3F14-40B8-A2B9-9F5C6516B5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9EF1BC-AE67-4200-9937-D6A8BD9C90FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,19 +331,19 @@
     <t>Blank</t>
   </si>
   <si>
-    <t>Intern</t>
+    <t>Mohamed Aslam</t>
   </si>
   <si>
-    <t>Tanushree</t>
+    <t>DC5046</t>
   </si>
   <si>
-    <t>DC4771</t>
+    <t>mohamed@qaoncloud.com</t>
   </si>
   <si>
-    <t>Suganya@qaoncloud.com</t>
+    <t>Opus Clip</t>
   </si>
   <si>
-    <t>Indihood</t>
+    <t>JrQAEngineer</t>
   </si>
 </sst>
 </file>
@@ -453,8 +453,9 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -519,7 +520,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -682,6 +683,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -770,78 +786,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -932,11 +876,83 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1207,206 +1223,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="23.4" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
-      <c r="AD1" s="48"/>
-      <c r="AE1" s="48"/>
-      <c r="AF1" s="48"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="62" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="64"/>
-      <c r="AS1" s="68" t="s">
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="AT1" s="69"/>
-      <c r="AU1" s="69"/>
-      <c r="AV1" s="69"/>
-      <c r="AW1" s="69"/>
-      <c r="AX1" s="69"/>
-      <c r="AY1" s="69"/>
-      <c r="AZ1" s="69"/>
-      <c r="BA1" s="69"/>
-      <c r="BB1" s="69"/>
-      <c r="BC1" s="69"/>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="74" t="s">
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
+      <c r="AV1" s="45"/>
+      <c r="AW1" s="45"/>
+      <c r="AX1" s="45"/>
+      <c r="AY1" s="45"/>
+      <c r="AZ1" s="45"/>
+      <c r="BA1" s="45"/>
+      <c r="BB1" s="45"/>
+      <c r="BC1" s="45"/>
+      <c r="BD1" s="46"/>
+      <c r="BE1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="75"/>
-      <c r="BH1" s="76"/>
-      <c r="BI1" s="80" t="s">
+      <c r="BF1" s="51"/>
+      <c r="BG1" s="51"/>
+      <c r="BH1" s="52"/>
+      <c r="BI1" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="81"/>
-      <c r="BK1" s="82"/>
-      <c r="BL1" s="50" t="s">
+      <c r="BJ1" s="57"/>
+      <c r="BK1" s="58"/>
+      <c r="BL1" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="51"/>
-      <c r="BN1" s="52"/>
-      <c r="BO1" s="41" t="s">
+      <c r="BM1" s="81"/>
+      <c r="BN1" s="82"/>
+      <c r="BO1" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="41" t="s">
+      <c r="BP1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="BQ1" s="41" t="s">
+      <c r="BQ1" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="43" t="s">
+      <c r="BR1" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="45" t="s">
+      <c r="BS1" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="BT1" s="32" t="s">
+      <c r="BT1" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="BU1" s="33"/>
-      <c r="BV1" s="33"/>
-      <c r="BW1" s="33"/>
-      <c r="BX1" s="33"/>
-      <c r="BY1" s="34"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="64"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
       <c r="CB1" s="1"/>
     </row>
     <row r="2" spans="1:80" ht="21" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="35" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="35" t="s">
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="35" t="s">
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="37"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="67"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="35" t="s">
+      <c r="X2" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="65"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
-      <c r="AM2" s="66"/>
-      <c r="AN2" s="66"/>
-      <c r="AO2" s="66"/>
-      <c r="AP2" s="66"/>
-      <c r="AQ2" s="66"/>
-      <c r="AR2" s="67"/>
-      <c r="AS2" s="71"/>
-      <c r="AT2" s="72"/>
-      <c r="AU2" s="72"/>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="72"/>
-      <c r="AX2" s="72"/>
-      <c r="AY2" s="72"/>
-      <c r="AZ2" s="72"/>
-      <c r="BA2" s="72"/>
-      <c r="BB2" s="72"/>
-      <c r="BC2" s="72"/>
-      <c r="BD2" s="73"/>
-      <c r="BE2" s="77"/>
-      <c r="BF2" s="78"/>
-      <c r="BG2" s="78"/>
-      <c r="BH2" s="79"/>
-      <c r="BI2" s="83"/>
-      <c r="BJ2" s="84"/>
-      <c r="BK2" s="85"/>
-      <c r="BL2" s="53"/>
-      <c r="BM2" s="54"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="42"/>
-      <c r="BP2" s="42"/>
-      <c r="BQ2" s="42"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="46"/>
+      <c r="Y2" s="66"/>
+      <c r="Z2" s="66"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="67"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="42"/>
+      <c r="AL2" s="42"/>
+      <c r="AM2" s="42"/>
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="47"/>
+      <c r="AT2" s="48"/>
+      <c r="AU2" s="48"/>
+      <c r="AV2" s="48"/>
+      <c r="AW2" s="48"/>
+      <c r="AX2" s="48"/>
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="48"/>
+      <c r="BA2" s="48"/>
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="48"/>
+      <c r="BD2" s="49"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="54"/>
+      <c r="BG2" s="54"/>
+      <c r="BH2" s="55"/>
+      <c r="BI2" s="59"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="61"/>
+      <c r="BL2" s="83"/>
+      <c r="BM2" s="84"/>
+      <c r="BN2" s="85"/>
+      <c r="BO2" s="72"/>
+      <c r="BP2" s="72"/>
+      <c r="BQ2" s="72"/>
+      <c r="BR2" s="74"/>
+      <c r="BS2" s="76"/>
       <c r="BT2" s="3"/>
       <c r="BU2" s="4"/>
       <c r="BV2" s="5"/>
-      <c r="BW2" s="38" t="s">
+      <c r="BW2" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="BX2" s="39"/>
-      <c r="BY2" s="40"/>
+      <c r="BX2" s="69"/>
+      <c r="BY2" s="70"/>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1"/>
       <c r="CB2" s="1"/>
     </row>
-    <row r="3" spans="1:80" ht="75" customHeight="1">
+    <row r="3" spans="1:80" ht="75" customHeight="1" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1632,24 +1648,24 @@
       <c r="CA3" s="1"/>
       <c r="CB3" s="1"/>
     </row>
-    <row r="4" spans="1:80" ht="13.8">
+    <row r="4" spans="1:80" ht="27" thickBot="1">
       <c r="A4" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="C4" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="87">
+        <v>45690</v>
+      </c>
+      <c r="E4" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="87">
-        <v>45707</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="F4" s="86" t="s">
         <v>92</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>88</v>
       </c>
       <c r="G4" s="22">
         <v>60</v>
@@ -1838,7 +1854,7 @@
    F4="QAEngineer", IFERROR(BM4/BL4*35/100, 0),
    F4="QALead", IFERROR(BM4/BL4*20/100, 0)
 )</f>
-        <v>3.6923076923076927E-2</v>
+        <v>4.9230769230769231E-2</v>
       </c>
       <c r="BO4" s="17" cm="1">
         <f t="array" ref="BO4">_xlfn.IFS(
@@ -1848,7 +1864,7 @@
    F4="SrQAEngineer", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.4 / 100, 0),
    F4="QALead", IF(AND(BG4=0, BI4&gt;=0.5, BL4&gt;0, BM4&gt;0), (100 - SUM(BE4:BH4)) * 0.4 / 100, 0)
 )</f>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BP4" s="17" cm="1">
         <f t="array" ref="BP4">_xlfn.IFS(F4="Intern", (BI4*1)*10/100, F4="JrQAEngineer", (BI4*1)*10/100, F4="QAEngineer", (BI4*1)*5/100, F4="SrQAEngineer", (BI4*1)*5/100, F4="QALead", (BI4*1)*5/100)</f>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="BS4" s="17">
         <f t="shared" ref="BS4" si="2">SUM(BN4:BR4)</f>
-        <v>0.63692307692307693</v>
+        <v>0.5492307692307693</v>
       </c>
     </row>
     <row r="5" spans="1:80" ht="13.8">
@@ -28094,11 +28110,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="AI1:AR2"/>
-    <mergeCell ref="AS1:BD2"/>
-    <mergeCell ref="BE1:BH2"/>
-    <mergeCell ref="BI1:BK2"/>
     <mergeCell ref="BT1:BY1"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="M2:P2"/>
@@ -28112,9 +28123,14 @@
     <mergeCell ref="BS1:BS2"/>
     <mergeCell ref="G1:AH1"/>
     <mergeCell ref="BL1:BN2"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="AI1:AR2"/>
+    <mergeCell ref="AS1:BD2"/>
+    <mergeCell ref="BE1:BH2"/>
+    <mergeCell ref="BI1:BK2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E5" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{2840A0E8-1D80-4C36-9E5A-37EBA5ECD401}">
       <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
     </dataValidation>
   </dataValidations>
